--- a/data/trans_orig/P1402-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2007</t>
+          <t>Población con diagnóstico de diabetes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32826</t>
+          <t>31670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254734</t>
+          <t>255194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266681</t>
+          <t>267355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243167</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255713</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501022</t>
+          <t>502178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519596</t>
+          <t>520060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33431</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58961</t>
+          <t>57207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54050</t>
+          <t>53514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86822</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454818</t>
+          <t>456052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476153</t>
+          <t>475335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444988</t>
+          <t>446742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470518</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>910202</t>
+          <t>910153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942974</t>
+          <t>943510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290437</t>
+          <t>290577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307588</t>
+          <t>307636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302509</t>
+          <t>302796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320467</t>
+          <t>320598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598599</t>
+          <t>599085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624286</t>
+          <t>624044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>333389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348633</t>
+          <t>348554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340105</t>
+          <t>341071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358449</t>
+          <t>358131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680926</t>
+          <t>681924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703158</t>
+          <t>702962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17826</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29714</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185482</t>
+          <t>184615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197216</t>
+          <t>196612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177954</t>
+          <t>177515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>195446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367905</t>
+          <t>366359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389856</t>
+          <t>389772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>248664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262989</t>
+          <t>263031</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258051</t>
+          <t>258570</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271798</t>
+          <t>272046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513524</t>
+          <t>510910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532820</t>
+          <t>531277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>54573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105909</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561687</t>
+          <t>560454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585737</t>
+          <t>585761</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574832</t>
+          <t>575397</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602285</t>
+          <t>602226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1147337</t>
+          <t>1144665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1182895</t>
+          <t>1181461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63307</t>
+          <t>65119</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83853</t>
+          <t>81883</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123921</t>
+          <t>122654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>680488</t>
+          <t>678676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>705589</t>
+          <t>705750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714173</t>
+          <t>715761</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744671</t>
+          <t>744407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1403385</t>
+          <t>1404652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1443453</t>
+          <t>1445423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209270</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>201167</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259997</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>376434</t>
+          <t>380100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>453261</t>
+          <t>455760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3067273</t>
+          <t>3065741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3117822</t>
+          <t>3115502</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3119200</t>
+          <t>3120441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3177930</t>
+          <t>3178030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6202480</t>
+          <t>6199981</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6279307</t>
+          <t>6275641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2012</t>
+          <t>Población con diagnóstico de diabetes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>52918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261767</t>
+          <t>262434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281290</t>
+          <t>281913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258926</t>
+          <t>259278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276244</t>
+          <t>276105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528218</t>
+          <t>529065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553955</t>
+          <t>554394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50559</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>44168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73742</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>74468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115027</t>
+          <t>113193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454968</t>
+          <t>455416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480126</t>
+          <t>480073</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450023</t>
+          <t>450003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479874</t>
+          <t>479597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914265</t>
+          <t>916099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952561</t>
+          <t>954824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>53932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86301</t>
+          <t>85360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278440</t>
+          <t>279624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300852</t>
+          <t>301637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292067</t>
+          <t>292100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316806</t>
+          <t>315782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>578765</t>
+          <t>579706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611817</t>
+          <t>611134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>43978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73444</t>
+          <t>71387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340070</t>
+          <t>340642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359128</t>
+          <t>358762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343605</t>
+          <t>342940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366214</t>
+          <t>364797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689489</t>
+          <t>691546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720509</t>
+          <t>718955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35385</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>182616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200733</t>
+          <t>200521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179829</t>
+          <t>180283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200908</t>
+          <t>200333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371032</t>
+          <t>367689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396824</t>
+          <t>396720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62801</t>
+          <t>63558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243360</t>
+          <t>243556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260666</t>
+          <t>260658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238672</t>
+          <t>237968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258204</t>
+          <t>258493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>489276</t>
+          <t>488519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514777</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>41240</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70300</t>
+          <t>71555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45445</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75503</t>
+          <t>74497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92088</t>
+          <t>95152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132142</t>
+          <t>134884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592488</t>
+          <t>591233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621334</t>
+          <t>621548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618350</t>
+          <t>619356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>648408</t>
+          <t>648139</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1224499</t>
+          <t>1221757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1264553</t>
+          <t>1261489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63475</t>
+          <t>64531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78755</t>
+          <t>81268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118733</t>
+          <t>120829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712956</t>
+          <t>712621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>742919</t>
+          <t>742484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>759103</t>
+          <t>758047</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>786984</t>
+          <t>786905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1482943</t>
+          <t>1480847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1522921</t>
+          <t>1520408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>226149</t>
+          <t>226653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>290753</t>
+          <t>288927</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>274632</t>
+          <t>274080</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>340769</t>
+          <t>342156</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>517140</t>
+          <t>518037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>613135</t>
+          <t>611320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3136026</t>
+          <t>3137852</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3200630</t>
+          <t>3200126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3214329</t>
+          <t>3212942</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3280466</t>
+          <t>3281018</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6368742</t>
+          <t>6370557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6464737</t>
+          <t>6463840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2016</t>
+          <t>Población con diagnóstico de diabetes en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32855</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>24799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260906</t>
+          <t>262183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279736</t>
+          <t>280168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263777</t>
+          <t>263904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279841</t>
+          <t>279698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533020</t>
+          <t>533203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556452</t>
+          <t>556455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>53027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73892</t>
+          <t>72193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>76323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115981</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450179</t>
+          <t>449548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474713</t>
+          <t>474357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449192</t>
+          <t>450891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479215</t>
+          <t>479821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909678</t>
+          <t>909434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>947904</t>
+          <t>949336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296377</t>
+          <t>295801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309916</t>
+          <t>310104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300069</t>
+          <t>300567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320393</t>
+          <t>320167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602460</t>
+          <t>602650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>626554</t>
+          <t>627700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>58495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57099</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89679</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310645</t>
+          <t>311469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336237</t>
+          <t>336184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349047</t>
+          <t>349202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369791</t>
+          <t>369913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667568</t>
+          <t>669089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700148</t>
+          <t>701712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>190353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203593</t>
+          <t>204019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188677</t>
+          <t>190018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205680</t>
+          <t>206413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385083</t>
+          <t>384489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406756</t>
+          <t>406086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51756</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236078</t>
+          <t>234937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251499</t>
+          <t>251358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243253</t>
+          <t>243027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261544</t>
+          <t>261091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>484482</t>
+          <t>484892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508860</t>
+          <t>509169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>58676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94157</t>
+          <t>91262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,47 +9452,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>60780</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>44660</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>78586</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>8,79%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>60780</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>45764</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>76598</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112761</t>
+          <t>113333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161633</t>
+          <t>161908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>562401</t>
+          <t>565296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598823</t>
+          <t>597882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,47 +9565,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>630514</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>612708</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>646634</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>91,21%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>630514</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>614696</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>645530</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1186219</t>
+          <t>1185944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1235091</t>
+          <t>1234519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>58153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92612</t>
+          <t>92539</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>59307</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93912</t>
+          <t>94508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126049</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175384</t>
+          <t>171242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685971</t>
+          <t>686044</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>718366</t>
+          <t>720430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>732255</t>
+          <t>731659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>767575</t>
+          <t>766860</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1429366</t>
+          <t>1433508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1478701</t>
+          <t>1479219</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>267555</t>
+          <t>268492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>334290</t>
+          <t>332542</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>266253</t>
+          <t>263158</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>335160</t>
+          <t>337702</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>546898</t>
+          <t>548885</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>641709</t>
+          <t>646291</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3060060</t>
+          <t>3061808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3126795</t>
+          <t>3125858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3209382</t>
+          <t>3206840</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3278289</t>
+          <t>3281384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6297183</t>
+          <t>6292601</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6391994</t>
+          <t>6390007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2023</t>
+          <t>Población con diagnóstico de diabetes en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46524</t>
+          <t>46329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69148</t>
+          <t>68531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264919</t>
+          <t>265114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286602</t>
+          <t>286931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260507</t>
+          <t>260300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273023</t>
+          <t>272759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531929</t>
+          <t>532546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555774</t>
+          <t>555664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>56060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70355</t>
+          <t>70515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102846</t>
+          <t>103155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460936</t>
+          <t>461333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487614</t>
+          <t>488473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459506</t>
+          <t>459403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480313</t>
+          <t>480045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928838</t>
+          <t>928529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961329</t>
+          <t>961169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56106</t>
+          <t>54320</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80319</t>
+          <t>79910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>271649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289452</t>
+          <t>289725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308024</t>
+          <t>307346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324624</t>
+          <t>324201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584310</t>
+          <t>584719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608523</t>
+          <t>610309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>70102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274389</t>
+          <t>274843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>291978</t>
+          <t>292191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>438156</t>
+          <t>439357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459214</t>
+          <t>459647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720128</t>
+          <t>718172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749088</t>
+          <t>748362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33542</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>51964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156834</t>
+          <t>156097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167494</t>
+          <t>167526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174333</t>
+          <t>174581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186719</t>
+          <t>186692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334327</t>
+          <t>334653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351516</t>
+          <t>351425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>54254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76242</t>
+          <t>74608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222881</t>
+          <t>222766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239930</t>
+          <t>240262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224061</t>
+          <t>223254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236144</t>
+          <t>236170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449781</t>
+          <t>451415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472467</t>
+          <t>471769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70607</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58137</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60421</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119879</t>
+          <t>119536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>547401</t>
+          <t>545897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>574258</t>
+          <t>574918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>789934</t>
+          <t>790951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>830134</t>
+          <t>829615</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1346200</t>
+          <t>1346543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1405658</t>
+          <t>1412334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78274</t>
+          <t>79341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55398</t>
+          <t>57083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61216</t>
+          <t>63315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124137</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>850446</t>
+          <t>849379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>905856</t>
+          <t>903004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>659994</t>
+          <t>658309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>679185</t>
+          <t>679588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1519975</t>
+          <t>1519638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1582896</t>
+          <t>1580797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>231104</t>
+          <t>235490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>339721</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>215392</t>
+          <t>210216</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292618</t>
+          <t>294073</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>484173</t>
+          <t>484867</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>617312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3112279</t>
+          <t>3112379</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3220896</t>
+          <t>3216510</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3363877</t>
+          <t>3362422</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3441103</t>
+          <t>3446279</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6493521</t>
+          <t>6491183</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6624322</t>
+          <t>6623628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1402-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255194</t>
+          <t>254828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267355</t>
+          <t>267425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255058</t>
+          <t>255593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>502178</t>
+          <t>501960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520060</t>
+          <t>520649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>31575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>57928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>53520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86871</t>
+          <t>85980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456052</t>
+          <t>455677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475335</t>
+          <t>476907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446742</t>
+          <t>446021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471119</t>
+          <t>472374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>910153</t>
+          <t>911044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>943510</t>
+          <t>943504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55173</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290577</t>
+          <t>291819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307636</t>
+          <t>308251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302796</t>
+          <t>301722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320598</t>
+          <t>320643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>599085</t>
+          <t>599856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624044</t>
+          <t>623279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>29477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48203</t>
+          <t>49757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333389</t>
+          <t>333477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348554</t>
+          <t>348749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341071</t>
+          <t>341979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358131</t>
+          <t>357952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681924</t>
+          <t>680370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702962</t>
+          <t>704190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44617</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184615</t>
+          <t>184414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196612</t>
+          <t>196662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177515</t>
+          <t>176850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195446</t>
+          <t>195357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366359</t>
+          <t>367904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389772</t>
+          <t>388518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,82 +2463,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>11713</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19632</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>25275</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>15753</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>36636</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>11713</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>19574</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>25275</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>17678</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>38045</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248664</t>
+          <t>248259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263031</t>
+          <t>262998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,82 +2576,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>266431</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>258512</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>272115</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>523680</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>512319</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>533202</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>93,33%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>266431</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>258570</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>272046</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>523680</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>510910</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>531277</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54573</t>
+          <t>55046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>63598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>71008</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>105194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560454</t>
+          <t>559981</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585761</t>
+          <t>585078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>575397</t>
+          <t>574621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602226</t>
+          <t>601555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1144665</t>
+          <t>1148052</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1181461</t>
+          <t>1182238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>37656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65119</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>39546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81883</t>
+          <t>82790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122654</t>
+          <t>121128</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>678676</t>
+          <t>679278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>705750</t>
+          <t>706139</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>715761</t>
+          <t>715945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744407</t>
+          <t>743965</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1404652</t>
+          <t>1406178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1445423</t>
+          <t>1444516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>161041</t>
+          <t>163060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>210802</t>
+          <t>212361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258756</t>
+          <t>255318</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380100</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>455760</t>
+          <t>457589</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3065741</t>
+          <t>3064182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3115502</t>
+          <t>3113483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3120441</t>
+          <t>3123879</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3178030</t>
+          <t>3177658</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6199981</t>
+          <t>6198152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6275641</t>
+          <t>6277979</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262434</t>
+          <t>262215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281913</t>
+          <t>281752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259278</t>
+          <t>257531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276105</t>
+          <t>275886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529065</t>
+          <t>527151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554394</t>
+          <t>552939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>24543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44168</t>
+          <t>43944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>72405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113193</t>
+          <t>114547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455416</t>
+          <t>455982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480073</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450003</t>
+          <t>451360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>479821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916099</t>
+          <t>914745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954824</t>
+          <t>954025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53932</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85360</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>278913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301637</t>
+          <t>301470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292100</t>
+          <t>291988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315782</t>
+          <t>316127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>579706</t>
+          <t>580211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611134</t>
+          <t>613692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>72888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340642</t>
+          <t>339882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358762</t>
+          <t>358824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>344103</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364797</t>
+          <t>365776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691546</t>
+          <t>690045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718955</t>
+          <t>720472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>38510</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64520</t>
+          <t>61924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182616</t>
+          <t>183221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200521</t>
+          <t>200552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180283</t>
+          <t>181081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200333</t>
+          <t>200868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367689</t>
+          <t>370285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396720</t>
+          <t>396704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40128</t>
+          <t>39561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>36805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63558</t>
+          <t>64121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243556</t>
+          <t>243410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260658</t>
+          <t>260931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237968</t>
+          <t>238535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258493</t>
+          <t>258291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488519</t>
+          <t>487956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515344</t>
+          <t>515272</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>40460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>69148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45714</t>
+          <t>45507</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74497</t>
+          <t>73569</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95152</t>
+          <t>93114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134884</t>
+          <t>133333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591233</t>
+          <t>593640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621548</t>
+          <t>622328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619356</t>
+          <t>620284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>648139</t>
+          <t>648346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1221757</t>
+          <t>1223308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1261489</t>
+          <t>1263527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>64564</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35999</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64531</t>
+          <t>63763</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81268</t>
+          <t>79747</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120829</t>
+          <t>121622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712621</t>
+          <t>714534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>742484</t>
+          <t>743209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>758047</t>
+          <t>758815</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>786905</t>
+          <t>786579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1480847</t>
+          <t>1480054</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1520408</t>
+          <t>1521929</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>226653</t>
+          <t>226560</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288927</t>
+          <t>292023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>274080</t>
+          <t>273925</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>342156</t>
+          <t>343177</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>518037</t>
+          <t>521469</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>611320</t>
+          <t>609828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3137852</t>
+          <t>3134756</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3200126</t>
+          <t>3200219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3212942</t>
+          <t>3211921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3281018</t>
+          <t>3281173</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6370557</t>
+          <t>6372049</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6463840</t>
+          <t>6460408</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262183</t>
+          <t>260156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280168</t>
+          <t>280785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263904</t>
+          <t>264605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279698</t>
+          <t>279764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533203</t>
+          <t>532654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556455</t>
+          <t>555710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>27903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72193</t>
+          <t>71964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76323</t>
+          <t>76691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>114240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449548</t>
+          <t>451506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>474357</t>
+          <t>474672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450891</t>
+          <t>451120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479821</t>
+          <t>480979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909434</t>
+          <t>911419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949336</t>
+          <t>948968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295801</t>
+          <t>296866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310104</t>
+          <t>309581</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300567</t>
+          <t>299596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320167</t>
+          <t>320203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602650</t>
+          <t>602200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627700</t>
+          <t>626336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58495</t>
+          <t>57901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38081</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>56624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>88275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311469</t>
+          <t>312063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336184</t>
+          <t>336813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349202</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369913</t>
+          <t>369540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>669089</t>
+          <t>668972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701712</t>
+          <t>700623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28569</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45319</t>
+          <t>43868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190353</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204019</t>
+          <t>203971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190018</t>
+          <t>189811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>206581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384489</t>
+          <t>385940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406086</t>
+          <t>408044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234937</t>
+          <t>236132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251358</t>
+          <t>251228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243027</t>
+          <t>243023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261091</t>
+          <t>261626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>484892</t>
+          <t>486418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509169</t>
+          <t>509386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58676</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91262</t>
+          <t>91796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44660</t>
+          <t>44477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78586</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113333</t>
+          <t>113109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161908</t>
+          <t>160711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565296</t>
+          <t>564762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597882</t>
+          <t>598937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>612708</t>
+          <t>612351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>646634</t>
+          <t>646817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1185944</t>
+          <t>1187141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1234519</t>
+          <t>1234743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58153</t>
+          <t>60191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59307</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94508</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125531</t>
+          <t>124842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171242</t>
+          <t>173155</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>686044</t>
+          <t>687765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720430</t>
+          <t>718392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731659</t>
+          <t>732868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>766860</t>
+          <t>767757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1433508</t>
+          <t>1431595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1479219</t>
+          <t>1479908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>268492</t>
+          <t>266855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>332542</t>
+          <t>331080</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>297179</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>262473</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>336372</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>594895</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>548676</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>639499</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>297179</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>263158</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>337702</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>594895</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>548885</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>646291</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3061808</t>
+          <t>3063270</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3125858</t>
+          <t>3127495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3206840</t>
+          <t>3208170</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3281384</t>
+          <t>3282069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6292601</t>
+          <t>6299393</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6390007</t>
+          <t>6390216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46329</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>59977</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>48306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>278020</t>
+          <t>283603</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265114</t>
+          <t>272219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286931</t>
+          <t>293119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>267313</t>
+          <t>291326</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260300</t>
+          <t>284003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272759</t>
+          <t>297404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>545332</t>
+          <t>574929</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532546</t>
+          <t>562427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555664</t>
+          <t>586600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>55900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43467</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>35538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84930</t>
+          <t>87433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70515</t>
+          <t>71745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103155</t>
+          <t>104196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>475930</t>
+          <t>487399</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461333</t>
+          <t>473760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488473</t>
+          <t>499741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>470824</t>
+          <t>500637</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459403</t>
+          <t>491332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480045</t>
+          <t>510271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>946754</t>
+          <t>988036</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928529</t>
+          <t>971273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961169</t>
+          <t>1003724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43852</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>25583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66657</t>
+          <t>66673</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54320</t>
+          <t>55112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79910</t>
+          <t>78679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281434</t>
+          <t>281717</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271649</t>
+          <t>272503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289725</t>
+          <t>290163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>316538</t>
+          <t>323425</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307346</t>
+          <t>314343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324201</t>
+          <t>330798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>597972</t>
+          <t>605142</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584719</t>
+          <t>593136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610309</t>
+          <t>616703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36361</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54492</t>
+          <t>62029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>50522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70102</t>
+          <t>77027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>284861</t>
+          <t>340312</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274843</t>
+          <t>327240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292191</t>
+          <t>349359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>448922</t>
+          <t>392766</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439357</t>
+          <t>384173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459647</t>
+          <t>399511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>733782</t>
+          <t>733078</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718172</t>
+          <t>718080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748362</t>
+          <t>744585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>22531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43086</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51964</t>
+          <t>55100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>162850</t>
+          <t>188919</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156097</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167526</t>
+          <t>194208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>180681</t>
+          <t>197825</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174581</t>
+          <t>190875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186692</t>
+          <t>203892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>343531</t>
+          <t>386744</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334653</t>
+          <t>376987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351425</t>
+          <t>395477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37888</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63474</t>
+          <t>64868</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>77567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232019</t>
+          <t>232819</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222766</t>
+          <t>223700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240262</t>
+          <t>240676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>230530</t>
+          <t>236119</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223254</t>
+          <t>229639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236170</t>
+          <t>242214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>462549</t>
+          <t>468938</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451415</t>
+          <t>456239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471769</t>
+          <t>479365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>85616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40124</t>
+          <t>51229</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>41118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57120</t>
+          <t>62742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>101198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119536</t>
+          <t>140422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>562020</t>
+          <t>645187</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545897</t>
+          <t>627728</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>574918</t>
+          <t>659904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>807947</t>
+          <t>719456</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>790951</t>
+          <t>707943</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>829615</t>
+          <t>729567</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1369967</t>
+          <t>1364643</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1346543</t>
+          <t>1343607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1412334</t>
+          <t>1382831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>618008</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618008</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618008</t>
+          <t>713344</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848071</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848071</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848071</t>
+          <t>770685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466079</t>
+          <t>1484029</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466079</t>
+          <t>1484029</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466079</t>
+          <t>1484029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53723</t>
+          <t>61317</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57083</t>
+          <t>66031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>99192</t>
+          <t>114264</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>96243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>133124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>874997</t>
+          <t>736755</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>849379</t>
+          <t>721743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>903004</t>
+          <t>748344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>777661</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658309</t>
+          <t>764578</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>679588</t>
+          <t>788036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1544920</t>
+          <t>1514417</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1519638</t>
+          <t>1495557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1580797</t>
+          <t>1532438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>235490</t>
+          <t>295171</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>339621</t>
+          <t>360639</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210216</t>
+          <t>265737</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294073</t>
+          <t>316192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>484867</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>617312</t>
+          <t>656432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>7,93%</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3152131</t>
+          <t>3196711</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3112379</t>
+          <t>3164232</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3216510</t>
+          <t>3229700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3392676</t>
+          <t>3439215</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3362422</t>
+          <t>3414837</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3446279</t>
+          <t>3465292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6544807</t>
+          <t>6635926</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6491183</t>
+          <t>6599468</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6623628</t>
+          <t>6680475</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>92,07%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
